--- a/consent_forms/015_ai_ethics_licensing_form--consent_forms.xlsx
+++ b/consent_forms/015_ai_ethics_licensing_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -998,12 +998,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'for-profit_corporation',_'value':_'for_profit'}</t>
+          <t>for-profit_corporation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'For-Profit Corporation', 'value': 'for_profit'}</t>
+          <t>For-Profit Corporation</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'non-profit_/_ngo',_'value':_'non_profit'}</t>
+          <t>non-profit_/_ngo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Non-Profit / NGO', 'value': 'non_profit'}</t>
+          <t>Non-Profit / NGO</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'academic_/_research_institution',_'value':_'academic'}</t>
+          <t>academic_/_research_institution</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Academic / Research Institution', 'value': 'academic'}</t>
+          <t>Academic / Research Institution</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'individual_developer',_'value':_'individual'}</t>
+          <t>individual_developer</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Individual Developer', 'value': 'individual'}</t>
+          <t>Individual Developer</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'government_agency',_'value':_'government'}</t>
+          <t>government_agency</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Government Agency', 'value': 'government'}</t>
+          <t>Government Agency</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'commercial_enterprise_license',_'value':_'commercial'}</t>
+          <t>commercial_enterprise_license</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Commercial Enterprise License', 'value': 'commercial'}</t>
+          <t>Commercial Enterprise License</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'research_and_development_license',_'value':_'research'}</t>
+          <t>research_and_development_license</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Research and Development License', 'value': 'research'}</t>
+          <t>Research and Development License</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'educational_/_non-commercial_license',_'value':_'educational'}</t>
+          <t>educational_/_non-commercial_license</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Educational / Non-Commercial License', 'value': 'educational'}</t>
+          <t>Educational / Non-Commercial License</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'evaluation_/_trial_license',_'value':_'evaluation'}</t>
+          <t>evaluation_/_trial_license</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Evaluation / Trial License', 'value': 'evaluation'}</t>
+          <t>Evaluation / Trial License</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'lethal_autonomous_weapons_systems',_'value':_'weapons'}</t>
+          <t>lethal_autonomous_weapons_systems</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Lethal Autonomous Weapons Systems', 'value': 'weapons'}</t>
+          <t>Lethal Autonomous Weapons Systems</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'mass_surveillance_or_social_scoring',_'value':_'surveillance'}</t>
+          <t>mass_surveillance_or_social_scoring</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Mass Surveillance or Social Scoring', 'value': 'surveillance'}</t>
+          <t>Mass Surveillance or Social Scoring</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'generating_misinformation_/_deepfakes_without_disclosure',_'value':_'misinformation'}</t>
+          <t>generating_misinformation_/_deepfakes_without_disclosure</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Generating Misinformation / Deepfakes without Disclosure', 'value': 'misinformation'}</t>
+          <t>Generating Misinformation / Deepfakes without Disclosure</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'discrimination_in_hiring,_credit,_or_healthcare',_'value':_'discrimination'}</t>
+          <t>discrimination_in_hiring,_credit,_or_healthcare</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Discrimination in Hiring, Credit, or Healthcare', 'value': 'discrimination'}</t>
+          <t>Discrimination in Hiring, Credit, or Healthcare</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'exploitation_of_vulnerable_groups',_'value':_'exploitation'}</t>
+          <t>exploitation_of_vulnerable_groups</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Exploitation of Vulnerable Groups', 'value': 'exploitation'}</t>
+          <t>Exploitation of Vulnerable Groups</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'gdpr_(eu)',_'value':_'gdpr'}</t>
+          <t>gdpr_(eu)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'GDPR (EU)', 'value': 'gdpr'}</t>
+          <t>GDPR (EU)</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'ccpa/cpra_(california)',_'value':_'ccpa'}</t>
+          <t>ccpa/cpra_(california)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'CCPA/CPRA (California)', 'value': 'ccpa'}</t>
+          <t>CCPA/CPRA (California)</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'hipaa_(healthcare_us)',_'value':_'hipaa'}</t>
+          <t>hipaa_(healthcare_us)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'HIPAA (Healthcare US)', 'value': 'hipaa'}</t>
+          <t>HIPAA (Healthcare US)</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'soc_2_type_ii',_'value':_'soc2'}</t>
+          <t>soc_2_type_ii</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'SOC 2 Type II', 'value': 'soc2'}</t>
+          <t>SOC 2 Type II</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'local_privacy_laws_only',_'value':_'local'}</t>
+          <t>local_privacy_laws_only</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Local Privacy Laws Only', 'value': 'local'}</t>
+          <t>Local Privacy Laws Only</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'fully_transparent_(open_weights/source)',_'value':_'open'}</t>
+          <t>fully_transparent_(open_weights/source)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Fully Transparent (Open Weights/Source)', 'value': 'open'}</t>
+          <t>Fully Transparent (Open Weights/Source)</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'partially_transparent_(api_access_+_documentation)',_'value':_'partial'}</t>
+          <t>partially_transparent_(api_access_+_documentation)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Partially Transparent (API access + Documentation)', 'value': 'partial'}</t>
+          <t>Partially Transparent (API access + Documentation)</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'proprietary_/_black_box',_'value':_'proprietary'}</t>
+          <t>proprietary_/_black_box</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Proprietary / Black Box', 'value': 'proprietary'}</t>
+          <t>Proprietary / Black Box</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'quarterly_self-assessment',_'value':_'quarterly'}</t>
+          <t>quarterly_self-assessment</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Quarterly Self-Assessment', 'value': 'quarterly'}</t>
+          <t>Quarterly Self-Assessment</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'annual_external_audit',_'value':_'annual'}</t>
+          <t>annual_external_audit</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Annual External Audit', 'value': 'annual'}</t>
+          <t>Annual External Audit</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'continuous_monitoring_(api_logs)',_'value':_'continuous'}</t>
+          <t>continuous_monitoring_(api_logs)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Continuous Monitoring (API logs)', 'value': 'continuous'}</t>
+          <t>Continuous Monitoring (API logs)</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'yes,_i_accept',_'value':_true}</t>
+          <t>yes,_i_accept</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Yes, I accept', 'value': True}</t>
+          <t>Yes, I accept</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'no,_i_do_not_accept',_'value':_false}</t>
+          <t>no,_i_do_not_accept</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'No, I do not accept', 'value': False}</t>
+          <t>No, I do not accept</t>
         </is>
       </c>
     </row>
